--- a/data/trans_orig/IP07C15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C15-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32789</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22726</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37315</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39622</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37692</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52567</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73091</t>
+          <t>72613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>55601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76422</t>
+          <t>75378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30080</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>37095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>44012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>60711</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18801</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>84300</t>
+          <t>83157</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>108611</t>
+          <t>109475</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>83989</t>
+          <t>83920</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>109809</t>
+          <t>109233</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>175223</t>
+          <t>173780</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>212649</t>
+          <t>212029</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>96911</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>122204</t>
+          <t>122621</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>115616</t>
+          <t>115497</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>142486</t>
+          <t>142666</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>218257</t>
+          <t>218628</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>258391</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41742</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>61788</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>49302</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>71485</t>
+          <t>72245</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>97277</t>
+          <t>97461</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>127486</t>
+          <t>128345</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14930</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>33883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41537</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32398</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46658</t>
+          <t>46699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>37414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>73665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96827</t>
+          <t>96476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38384</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28918</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44894</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76774</t>
+          <t>77470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53785</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>72881</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22926</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67230</t>
+          <t>67260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>108635</t>
+          <t>109213</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>137230</t>
+          <t>136880</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>112368</t>
+          <t>112843</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>139536</t>
+          <t>140641</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>229398</t>
+          <t>228882</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>269421</t>
+          <t>268441</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>98953</t>
+          <t>98503</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>126202</t>
+          <t>125847</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109924</t>
+          <t>110322</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>137915</t>
+          <t>137951</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>214875</t>
+          <t>216067</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>254355</t>
+          <t>256090</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>68150</t>
+          <t>67405</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>37885</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>58409</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>89604</t>
+          <t>89069</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>119889</t>
+          <t>118353</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -11431,12 +11431,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>33395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58451</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -12113,12 +12113,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46910</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43673</t>
+          <t>44481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63476</t>
+          <t>62740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86288</t>
+          <t>85662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58302</t>
+          <t>59559</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>57399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86892</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109926</t>
+          <t>112181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>46529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -13590,12 +13590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37729</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75737</t>
+          <t>74349</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>842</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -14272,12 +14272,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14400,12 +14400,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14435,12 +14435,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>94516</t>
+          <t>95754</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>123065</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>104893</t>
+          <t>104921</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>134424</t>
+          <t>132614</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>207588</t>
+          <t>208515</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>247886</t>
+          <t>250920</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>137324</t>
+          <t>137372</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>166660</t>
+          <t>168656</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>143258</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>175223</t>
+          <t>174462</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>290005</t>
+          <t>290558</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>333086</t>
+          <t>333287</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>73668</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>90232</t>
+          <t>89225</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>122150</t>
+          <t>121753</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15792,12 +15792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -15807,12 +15807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>44086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15955,12 +15955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -16474,12 +16474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>35999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16602,12 +16602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -17234,12 +17234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17382,12 +17382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17417,12 +17417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47334</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75658</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -17916,12 +17916,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59276</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17951,12 +17951,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17966,12 +17966,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17986,12 +17986,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98863</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26746</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>34282</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -18485,12 +18485,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18520,12 +18520,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41286</t>
+          <t>45076</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18555,12 +18555,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18598,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18613,12 +18613,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18668,12 +18668,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>52345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18683,12 +18683,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18726,12 +18726,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18761,12 +18761,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18796,12 +18796,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19237,12 +19237,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19252,12 +19252,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19315,12 +19315,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19365,12 +19365,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19428,12 +19428,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19443,12 +19443,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -19849,12 +19849,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>110450</t>
+          <t>108826</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>149040</t>
+          <t>148320</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19919,12 +19919,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>159076</t>
+          <t>163648</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>227087</t>
+          <t>229445</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>142140</t>
+          <t>146938</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>81528</t>
+          <t>83740</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>116650</t>
+          <t>118196</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>182808</t>
+          <t>183141</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>261532</t>
+          <t>259320</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31436</t>
+          <t>32025</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49104</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>40660</t>
+          <t>40721</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -20341,7 +20341,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
